--- a/SantanderCS/results/ResultListByTestModel_ejm.xlsx
+++ b/SantanderCS/results/ResultListByTestModel_ejm.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\big20\git\big20-ML-project2-team3\SantanderCS\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53BBC46A-A96A-4C90-AEF2-96684CDA9B9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A80E196E-A27E-4988-B1DC-C15322936033}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-60" yWindow="405" windowWidth="27270" windowHeight="14190" xr2:uid="{C44A7696-4C41-4B13-A873-C291A9185DA3}"/>
+    <workbookView xWindow="285" yWindow="1050" windowWidth="27270" windowHeight="14190" xr2:uid="{C44A7696-4C41-4B13-A873-C291A9185DA3}"/>
   </bookViews>
   <sheets>
     <sheet name="ejm" sheetId="3" r:id="rId1"/>
@@ -267,7 +267,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -430,13 +430,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -547,6 +556,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -938,7 +953,7 @@
       <c r="I2" s="31" t="s">
         <v>23</v>
       </c>
-      <c r="J2" s="24" t="s">
+      <c r="J2" s="38" t="s">
         <v>24</v>
       </c>
     </row>
@@ -970,6 +985,7 @@
       <c r="I3" s="33" t="s">
         <v>26</v>
       </c>
+      <c r="J3" s="37"/>
     </row>
     <row r="4" spans="1:10" ht="99.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="32">
@@ -999,6 +1015,7 @@
       <c r="I4" s="33" t="s">
         <v>29</v>
       </c>
+      <c r="J4" s="37"/>
     </row>
     <row r="5" spans="1:10" ht="99.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="32">
@@ -1028,6 +1045,7 @@
       <c r="I5" s="33" t="s">
         <v>32</v>
       </c>
+      <c r="J5" s="37"/>
     </row>
     <row r="6" spans="1:10" ht="147.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="32">
@@ -1057,6 +1075,7 @@
       <c r="I6" s="33" t="s">
         <v>34</v>
       </c>
+      <c r="J6" s="37"/>
     </row>
     <row r="7" spans="1:10" ht="99.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="32"/>
@@ -1084,6 +1103,7 @@
       <c r="I7" s="33" t="s">
         <v>36</v>
       </c>
+      <c r="J7" s="37"/>
     </row>
     <row r="8" spans="1:10" ht="99.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="32"/>
@@ -4276,6 +4296,9 @@
       <c r="I297" s="35"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="J2:J7"/>
+  </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
